--- a/tests/sample_data/CEData_Longline.xlsx
+++ b/tests/sample_data/CEData_Longline.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -412,10 +412,10 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -423,27 +423,27 @@
         </is>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>-15</v>
+        <v>-40</v>
       </c>
       <c r="G2">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="H2">
-        <v>2083</v>
+        <v>2903</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>1965</v>
+        <v>1974</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -451,24 +451,27 @@
         </is>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F3">
-        <v>-15</v>
+        <v>-5</v>
       </c>
       <c r="G3">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="H3">
-        <v>9647</v>
+        <v>145342</v>
+      </c>
+      <c r="I3">
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>1965</v>
+        <v>1975</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -476,27 +479,27 @@
         </is>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>-15</v>
+        <v>-40</v>
       </c>
       <c r="G4">
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="H4">
-        <v>91431</v>
+        <v>138142</v>
       </c>
       <c r="I4">
-        <v>525</v>
+        <v>532</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>1965</v>
+        <v>1975</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -504,47 +507,446 @@
         </is>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>-10</v>
+        <v>-25</v>
       </c>
       <c r="G5">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="H5">
-        <v>23560</v>
-      </c>
-      <c r="I5">
-        <v>56</v>
+        <v>2838</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>1965</v>
+        <v>1977</v>
       </c>
       <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="E6">
+        <v>7</v>
+      </c>
+      <c r="F6">
+        <v>-50</v>
+      </c>
+      <c r="G6">
+        <v>150</v>
+      </c>
+      <c r="H6">
+        <v>9266</v>
+      </c>
+      <c r="I6">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>1978</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="E7">
+        <v>8</v>
+      </c>
+      <c r="F7">
+        <v>-40</v>
+      </c>
+      <c r="G7">
+        <v>105</v>
+      </c>
+      <c r="H7">
+        <v>7357</v>
+      </c>
+      <c r="I7">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>1981</v>
+      </c>
+      <c r="B8">
+        <v>3</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="E8">
+        <v>9</v>
+      </c>
+      <c r="F8">
+        <v>-40</v>
+      </c>
+      <c r="G8">
+        <v>-10</v>
+      </c>
+      <c r="H8">
+        <v>12600</v>
+      </c>
+      <c r="I8">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>1981</v>
+      </c>
+      <c r="B9">
+        <v>5</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="E9">
+        <v>9</v>
+      </c>
+      <c r="F9">
+        <v>-35</v>
+      </c>
+      <c r="G9">
+        <v>-10</v>
+      </c>
+      <c r="H9">
+        <v>198674</v>
+      </c>
+      <c r="I9">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>1982</v>
+      </c>
+      <c r="B10">
+        <v>8</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="E10">
+        <v>4</v>
+      </c>
+      <c r="F10">
+        <v>-30</v>
+      </c>
+      <c r="G10">
+        <v>160</v>
+      </c>
+      <c r="H10">
+        <v>26454</v>
+      </c>
+      <c r="I10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>1983</v>
+      </c>
+      <c r="B11">
+        <v>3</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="E11">
+        <v>10</v>
+      </c>
+      <c r="F11">
+        <v>-40</v>
+      </c>
+      <c r="G11">
+        <v>-45</v>
+      </c>
+      <c r="H11">
+        <v>45995</v>
+      </c>
+      <c r="I11">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>1986</v>
+      </c>
+      <c r="B12">
         <v>1</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>-10</v>
-      </c>
-      <c r="G6">
-        <v>105</v>
-      </c>
-      <c r="H6">
-        <v>31232</v>
-      </c>
-      <c r="I6">
-        <v>35</v>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="E12">
+        <v>8</v>
+      </c>
+      <c r="F12">
+        <v>-45</v>
+      </c>
+      <c r="G12">
+        <v>90</v>
+      </c>
+      <c r="H12">
+        <v>2884</v>
+      </c>
+      <c r="I12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>1994</v>
+      </c>
+      <c r="B13">
+        <v>4</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="E13">
+        <v>9</v>
+      </c>
+      <c r="F13">
+        <v>-40</v>
+      </c>
+      <c r="G13">
+        <v>30</v>
+      </c>
+      <c r="H13">
+        <v>23040</v>
+      </c>
+      <c r="I13">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>1996</v>
+      </c>
+      <c r="B14">
+        <v>4</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="E14">
+        <v>14</v>
+      </c>
+      <c r="F14">
+        <v>-25</v>
+      </c>
+      <c r="G14">
+        <v>50</v>
+      </c>
+      <c r="H14">
+        <v>264434</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>1998</v>
+      </c>
+      <c r="B15">
+        <v>3</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="E15">
+        <v>14</v>
+      </c>
+      <c r="F15">
+        <v>-30</v>
+      </c>
+      <c r="G15">
+        <v>20</v>
+      </c>
+      <c r="H15">
+        <v>2406</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>1998</v>
+      </c>
+      <c r="B16">
+        <v>12</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="E16">
+        <v>13</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>75</v>
+      </c>
+      <c r="H16">
+        <v>193509</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>2001</v>
+      </c>
+      <c r="B17">
+        <v>12</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="E17">
+        <v>12</v>
+      </c>
+      <c r="F17">
+        <v>-25</v>
+      </c>
+      <c r="G17">
+        <v>160</v>
+      </c>
+      <c r="H17">
+        <v>15835</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>2005</v>
+      </c>
+      <c r="B18">
+        <v>5</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="E18">
+        <v>7</v>
+      </c>
+      <c r="F18">
+        <v>-40</v>
+      </c>
+      <c r="G18">
+        <v>150</v>
+      </c>
+      <c r="H18">
+        <v>1329377</v>
+      </c>
+      <c r="I18">
+        <v>1565</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>2006</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="E19">
+        <v>2</v>
+      </c>
+      <c r="F19">
+        <v>-30</v>
+      </c>
+      <c r="G19">
+        <v>100</v>
+      </c>
+      <c r="H19">
+        <v>244390</v>
+      </c>
+      <c r="I19">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>2008</v>
+      </c>
+      <c r="B20">
+        <v>4</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="E20">
+        <v>9</v>
+      </c>
+      <c r="F20">
+        <v>-35</v>
+      </c>
+      <c r="G20">
+        <v>25</v>
+      </c>
+      <c r="H20">
+        <v>865330</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>2013</v>
+      </c>
+      <c r="B21">
+        <v>5</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="E21">
+        <v>7</v>
+      </c>
+      <c r="F21">
+        <v>-40</v>
+      </c>
+      <c r="G21">
+        <v>155</v>
+      </c>
+      <c r="H21">
+        <v>214500</v>
       </c>
     </row>
   </sheetData>
@@ -554,7 +956,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -659,6 +1061,261 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Country Code</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Taiwan, Fishing Entity of</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Country Code</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ZA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Species Code</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ALB</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Thunnus alalunga</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Species Code</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BET</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Thunnus obesus</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Species Code</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>BSH</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Prionace glauca</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Species Code</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>BWA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Hyperoglyphe antarctica</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Species Code</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>GAG</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Galeorhinus galeus</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Species Code</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>HAU</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Polyprion spp</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Species Code</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>LAG</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Lampris guttatus</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Species Code</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ruvettus pretiosus</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Species Code</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>SBF</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Thunnus maccoyii</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Species Code</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>SHX</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Squaliformes</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Species Code</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>TUN</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Thunnini</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Species Code</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>YFT</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Thunnus albacares</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Species Code</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>YTC</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Seriola lalandi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
